--- a/stories/arbres/ATOM-SEC.ADU.002-02.xlsx
+++ b/stories/arbres/ATOM-SEC.ADU.002-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Ava va au marché. Maman vient avec elle. Maman est l'accompagnant. Ava aime rester avec l'accompagnant. Elle marche à côté de maman. Maman tient la main. Les pieds d'Ava restent près. Ils voient des pommes. Ava reste avec maman. L'adulte connu est là. Ava sent la main. Elle est calme. Ils écoutent les voix. Ava reste près. Maman dit : tu restes avec moi. Ava hoche la tête. Elle sourit.</t>
+          <t>Ava va au marché. Maman vient avec elle. Maman est l'accompagnant. Ava aime rester avec l'accompagnant. Elle marche à côté de maman. Maman tient la main. Les pieds d'Ava restent près. Ils voient des pommes. Ava reste avec maman. L'adulte connu est là. Ava sent la main. Elle est calme. Ils écoutent les voix. Ava reste près. Tu restes avec moi. Ava hoche la tête. Elle sourit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Ava va au marché. Maman vient avec elle. Maman est l'accompagnant. Ava aime rester avec l'accompagnant. Elle marche à côté de maman. Maman tient la main. Les pieds d'Ava restent près. Ils voient des pommes. Ava reste avec maman. L'adulte connu est là. Ava sent la main. Elle est calme. Ils écoutent les voix. Ava reste près.
+maman|Tu restes avec moi.
+narrateur|Ava hoche la tête. Elle sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Ava est au marché. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1641,6 +1669,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Ava reste avec maman. L'accompagnant est là. La main est tenue.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1803,6 +1836,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Ava et maman prennent des pommes. Ils rentrent ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1965,6 +2003,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1983,7 +2026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2000,6 +2043,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.ADU.002-02.xlsx
+++ b/stories/arbres/ATOM-SEC.ADU.002-02.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,7 @@
 narrateur|Ava hoche la tête. Elle sourit.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1505,7 @@
           <t>narrateur|Ava est au marché. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1674,6 +1681,7 @@
           <t>narrateur|Ava reste avec maman. L'accompagnant est là. La main est tenue.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1841,6 +1849,7 @@
           <t>narrateur|Ava et maman prennent des pommes. Ils rentrent ensemble.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2008,6 +2017,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2026,7 +2036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2050,6 +2060,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2064,7 +2088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2251,6 +2275,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.ADU.002-02.xlsx
+++ b/stories/arbres/ATOM-SEC.ADU.002-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ava reste avec maman</t>
+          <t>Le panier et la main de maman</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Le panier d'osier gratte. Chouchou va au marché. Il reste avec maman, près des pommes.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Ava va au marché. Maman vient avec elle. Maman est l'accompagnant. Ava aime rester avec l'accompagnant. Elle marche à côté de maman. Maman tient la main. Les pieds d'Ava restent près. Ils voient des pommes. Ava reste avec maman. L'adulte connu est là. Ava sent la main. Elle est calme. Ils écoutent les voix. Ava reste près. Tu restes avec moi. Ava hoche la tête. Elle sourit.</t>
+          <t>Le panier d'osier gratte le rebord. Il sent encore la paille. Une orange ronde attend dans une cagette. Elle est lisse, et un peu froide. Dehors, le matin est doux. Une feuille sèche tourne sur le pas de la porte. Chouchou vit avec papa et maman. Le panier est prêt, Chouchou. On va au marché ? Oui. On y va ensemble. Tu restes avec maman. Oui, papa. En ce moment, Chouchou va au marché. Maman vient avec lui. Maman est l'accompagnant. Chouchou aime rester avec l'accompagnant. Il marche à côté de maman. Maman tient la main. Les pieds de Chouchou restent près. Le panier tape contre la jambe. Ils voient des pommes. Une pomme rouge brille. Ça sent la menthe, tout près. Elle est rouge, maman. Oui. Tu restes avec moi. Chouchou reste avec maman. L'adulte connu est là. Chouchou sent la main. La main est douce. Il est calme. Ils écoutent les voix. Les voix sont douces, tout près. Une cagette claque, puis s'arrête. Tu as entendu la cagette ? Oui. Chouchou reste près. Je reste avec toi. Bravo. Tu restes à côté. On prend la pomme rouge ? Oui, maman. Maman pose la pomme dans le panier. Le panier penche un peu. Chouchou hoche la tête. Le panier gratte encore un peu.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,9 +1324,53 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Ava va au marché. Maman vient avec elle. Maman est l'accompagnant. Ava aime rester avec l'accompagnant. Elle marche à côté de maman. Maman tient la main. Les pieds d'Ava restent près. Ils voient des pommes. Ava reste avec maman. L'adulte connu est là. Ava sent la main. Elle est calme. Ils écoutent les voix. Ava reste près.
+          <t>narrateur|Le panier d'osier gratte le rebord.
+narrateur|Il sent encore la paille.
+narrateur|Une orange ronde attend dans une cagette.
+narrateur|Elle est lisse, et un peu froide.
+narrateur|Dehors, le matin est doux.
+narrateur|Une feuille sèche tourne sur le pas de la porte.
+narrateur|Chouchou vit avec papa et maman.
+papa|Le panier est prêt, Chouchou.
+enfant-m|On va au marché ?
+maman|Oui.
+maman|On y va ensemble.
+papa|Tu restes avec maman.
+enfant-m|Oui, papa.
+narrateur|En ce moment, Chouchou va au marché.
+narrateur|Maman vient avec lui.
+narrateur|Maman est l'accompagnant.
+narrateur|Chouchou aime rester avec l'accompagnant.
+narrateur|Il marche à côté de maman.
+narrateur|Maman tient la main.
+narrateur|Les pieds de Chouchou restent près.
+narrateur|Le panier tape contre la jambe.
+narrateur|Ils voient des pommes.
+narrateur|Une pomme rouge brille.
+narrateur|Ça sent la menthe, tout près.
+enfant-m|Elle est rouge, maman.
+maman|Oui.
 maman|Tu restes avec moi.
-narrateur|Ava hoche la tête. Elle sourit.</t>
+narrateur|Chouchou reste avec maman.
+narrateur|L'adulte connu est là.
+narrateur|Chouchou sent la main.
+narrateur|La main est douce.
+narrateur|Il est calme.
+narrateur|Ils écoutent les voix.
+narrateur|Les voix sont douces, tout près.
+narrateur|Une cagette claque, puis s'arrête.
+maman|Tu as entendu la cagette ?
+enfant-m|Oui.
+narrateur|Chouchou reste près.
+enfant-m|Je reste avec toi.
+maman|Bravo.
+maman|Tu restes à côté.
+maman|On prend la pomme rouge ?
+enfant-m|Oui, maman.
+narrateur|Maman pose la pomme dans le panier.
+narrateur|Le panier penche un peu.
+narrateur|Chouchou hoche la tête.
+narrateur|Le panier gratte encore un peu.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1342,7 +1398,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Ava est au marché. Que fait-elle ?</t>
+          <t>Chouchou est au marché. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1502,7 +1558,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Ava est au marché. Que fait-elle ?</t>
+          <t>narrateur|Chouchou est au marché.
+narrateur|Que fait-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1530,7 +1587,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Ava reste avec maman. L'accompagnant est là. La main est tenue.</t>
+          <t>Chouchou reste avec maman. L'accompagnant est là. La main est tenue. Tu restes avec moi ? Oui, maman. Bravo, Chouchou. Tu restes avec l'adulte connu. La pomme rouge brille encore. La paille sent encore le soleil. Je reste près. Oui. C'est bien.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1678,7 +1735,18 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Ava reste avec maman. L'accompagnant est là. La main est tenue.</t>
+          <t>narrateur|Chouchou reste avec maman.
+narrateur|L'accompagnant est là.
+narrateur|La main est tenue.
+maman|Tu restes avec moi ?
+enfant-m|Oui, maman.
+maman|Bravo, Chouchou.
+maman|Tu restes avec l'adulte connu.
+narrateur|La pomme rouge brille encore.
+narrateur|La paille sent encore le soleil.
+enfant-m|Je reste près.
+maman|Oui.
+maman|C'est bien.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1706,7 +1774,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Ava et maman prennent des pommes. Ils rentrent ensemble.</t>
+          <t>Chouchou et maman prennent des pommes. On rentre ensemble ? Oui. Ils rentrent ensemble. Le panier penche un peu. Papa ouvre la porte. Vous voilà. Tu es resté avec maman ? Oui, papa. Bravo. Tu as fait du bon travail. La main était tenue. La pomme était rouge. Oui. Le panier sent les pommes. L'orange de la cagette reste au marché.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1846,7 +1914,22 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Ava et maman prennent des pommes. Ils rentrent ensemble.</t>
+          <t>narrateur|Chouchou et maman prennent des pommes.
+maman|On rentre ensemble ?
+enfant-m|Oui.
+narrateur|Ils rentrent ensemble.
+narrateur|Le panier penche un peu.
+narrateur|Papa ouvre la porte.
+papa|Vous voilà.
+papa|Tu es resté avec maman ?
+enfant-m|Oui, papa.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+maman|La main était tenue.
+enfant-m|La pomme était rouge.
+papa|Oui.
+narrateur|Le panier sent les pommes.
+narrateur|L'orange de la cagette reste au marché.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1874,7 +1957,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Je suis resté avec maman. Bravo. Tu as fait du bon travail. Le panier sent les pommes. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2014,7 +2097,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Je suis resté avec maman.
+maman|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|Le panier sent les pommes.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2036,7 +2123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2074,6 +2161,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.ADU.002-02.xlsx
+++ b/stories/arbres/ATOM-SEC.ADU.002-02.xlsx
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Ava va au marché. Maman vient avec elle. Maman est l'accompagnant. Ava aime &lt;emphasis level="moderate"&gt;rester&lt;/emphasis&gt; avec l'accompagnant. Elle marche à côté de maman. Maman tient la main. Les pieds d'Ava restent près. Ils voient des pommes. Ava reste avec maman. L'adulte connu est là. Ava sent la main. Elle est calme. Ils écoutent les voix. Ava reste près. Maman dit : tu restes avec moi. Ava hoche la tête. Elle sourit.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le panier d'osier gratte le rebord. Il sent encore la paille. Une orange ronde attend dans une cagette. Elle est lisse, et un peu froide. Dehors, le matin est doux. Une feuille sèche tourne sur le pas de la porte. Chouchou vit avec papa et maman. Le panier est prêt, Chouchou. On va au marché ? Oui. On y va ensemble. Tu restes avec maman. Oui, papa. En ce moment, Chouchou va au marché. Maman vient avec lui. Maman est l'accompagnant. Chouchou aime rester avec l'accompagnant. Il marche à côté de maman. Maman tient la main. Les pieds de Chouchou restent près. Le panier tape contre la jambe. Ils voient des pommes. Une pomme rouge brille. Ça sent la menthe, tout près. Elle est rouge, maman. Oui. Tu restes avec moi. Chouchou reste avec maman. L'adulte connu est là. Chouchou sent la main. La main est douce. Il est calme. Ils écoutent les voix. Les voix sont douces, tout près. Une cagette claque, puis s'arrête. Tu as entendu la cagette ? Oui. Chouchou reste près. Je reste avec toi. Bravo. Tu restes à côté. On prend la pomme rouge ? Oui, maman. Maman pose la pomme dans le panier. Le panier penche un peu. Chouchou hoche la tête. Le panier gratte encore un peu.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1373,7 +1373,6 @@
 narrateur|Le panier gratte encore un peu.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1403,7 +1402,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Ava est au marché. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Chouchou est au marché. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1562,7 +1561,6 @@
 narrateur|Que fait-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1592,7 +1590,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Ava reste avec maman. L'accompagnant est là. La &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; est tenue.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Chouchou reste avec maman. L'accompagnant est là. La main est tenue. Tu restes avec moi ? Oui, maman. Bravo, Chouchou. Tu restes avec l'adulte connu. La pomme rouge brille encore. La paille sent encore le soleil. Je reste près. Oui. C'est bien.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1749,7 +1747,6 @@
 maman|C'est bien.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1774,12 +1771,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Chouchou et maman prennent des pommes. On rentre ensemble ? Oui. Ils rentrent ensemble. Le panier penche un peu. Papa ouvre la porte. Vous voilà. Tu es resté avec maman ? Oui, papa. Bravo. Tu as fait du bon travail. La main était tenue. La pomme était rouge. Oui. Le panier sent les pommes. L'orange de la cagette reste au marché.</t>
+          <t>Chouchou et maman prennent des pommes. On rentre ensemble ? Oui. Ils rentrent ensemble. Le panier penche un peu. Papa ouvre la porte. Vous voilà. Tu es resté avec maman ? Oui, papa. Bravo. La main était tenue. La pomme était rouge. Oui. Le panier sent les pommes. L'orange de la cagette reste au marché.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Ava et maman prennent des pommes. Ils rentrent ensemble.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Chouchou et maman prennent des pommes. On rentre ensemble ? Oui. Ils rentrent ensemble. Le panier penche un peu. Papa ouvre la porte. Vous voilà. Tu es resté avec maman ? Oui, papa. Bravo. La main était tenue. La pomme était rouge. Oui. Le panier sent les pommes. L'orange de la cagette reste au marché.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1924,7 +1921,6 @@
 papa|Tu es resté avec maman ?
 enfant-m|Oui, papa.
 papa|Bravo.
-papa|Tu as fait du bon travail.
 maman|La main était tenue.
 enfant-m|La pomme était rouge.
 papa|Oui.
@@ -1932,7 +1928,6 @@
 narrateur|L'orange de la cagette reste au marché.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,12 +1952,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Je suis resté avec maman. Bravo. Tu as fait du bon travail. Le panier sent les pommes. L'histoire est finie.</t>
+          <t>Je suis resté avec maman. Bravo. Le panier sent les pommes.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Je suis resté avec maman. Bravo. Le panier sent les pommes.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2099,12 +2094,9 @@
         <is>
           <t>enfant-m|Je suis resté avec maman.
 maman|Bravo.
-papa|Tu as fait du bon travail.
-narrateur|Le panier sent les pommes.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le panier sent les pommes.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2123,7 +2115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2168,6 +2160,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.ADU.002-02.xlsx
+++ b/stories/arbres/ATOM-SEC.ADU.002-02.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>marché</t>
+          <t>maison puis marché</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ava, maman</t>
+          <t>Chouchou, maman, papa</t>
         </is>
       </c>
     </row>
